--- a/docs/StructureDefinition-br-core-practitioner.xlsx
+++ b/docs/StructureDefinition-br-core-practitioner.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$229</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T14:13:05-03:00</t>
+    <t>2025-08-18T16:48:33-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2847,6 +2850,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -3186,7 +3204,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3298,7 +3316,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -3412,7 +3430,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -3524,7 +3542,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>100</v>
       </c>
@@ -3638,7 +3656,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>106</v>
       </c>
@@ -3752,7 +3770,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>115</v>
       </c>
@@ -3866,7 +3884,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>123</v>
       </c>
@@ -3980,7 +3998,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -4092,7 +4110,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -4204,7 +4222,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>141</v>
       </c>
@@ -4316,7 +4334,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>151</v>
       </c>
@@ -4337,7 +4355,7 @@
         <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
@@ -4432,7 +4450,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
@@ -4544,7 +4562,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>160</v>
       </c>
@@ -4656,7 +4674,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
@@ -4772,7 +4790,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>179</v>
       </c>
@@ -4886,7 +4904,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>190</v>
       </c>
@@ -4998,7 +5016,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -5110,7 +5128,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>197</v>
       </c>
@@ -5226,7 +5244,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -5338,7 +5356,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>210</v>
       </c>
@@ -5450,7 +5468,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>214</v>
       </c>
@@ -5566,7 +5584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>224</v>
       </c>
@@ -5680,7 +5698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>231</v>
       </c>
@@ -5794,7 +5812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>239</v>
       </c>
@@ -5908,7 +5926,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>247</v>
       </c>
@@ -6024,7 +6042,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>257</v>
       </c>
@@ -6140,7 +6158,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>266</v>
       </c>
@@ -6256,7 +6274,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>278</v>
       </c>
@@ -6370,7 +6388,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>287</v>
       </c>
@@ -6482,7 +6500,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>296</v>
       </c>
@@ -6596,7 +6614,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>305</v>
       </c>
@@ -6708,7 +6726,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>309</v>
       </c>
@@ -6822,7 +6840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>315</v>
       </c>
@@ -6936,7 +6954,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>322</v>
       </c>
@@ -7050,7 +7068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>331</v>
       </c>
@@ -7164,7 +7182,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>338</v>
       </c>
@@ -7278,7 +7296,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>344</v>
       </c>
@@ -7299,7 +7317,7 @@
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>77</v>
@@ -7394,7 +7412,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>346</v>
       </c>
@@ -7506,7 +7524,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>347</v>
       </c>
@@ -7618,7 +7636,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>348</v>
       </c>
@@ -7734,7 +7752,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>349</v>
       </c>
@@ -7848,7 +7866,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>351</v>
       </c>
@@ -7960,7 +7978,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>352</v>
       </c>
@@ -8072,7 +8090,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>353</v>
       </c>
@@ -8188,7 +8206,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>354</v>
       </c>
@@ -8300,7 +8318,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>355</v>
       </c>
@@ -8412,7 +8430,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>356</v>
       </c>
@@ -8528,7 +8546,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>357</v>
       </c>
@@ -8642,7 +8660,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>358</v>
       </c>
@@ -8756,7 +8774,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>359</v>
       </c>
@@ -8870,7 +8888,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>360</v>
       </c>
@@ -8986,7 +9004,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>361</v>
       </c>
@@ -9102,7 +9120,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>362</v>
       </c>
@@ -9218,7 +9236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>364</v>
       </c>
@@ -9332,7 +9350,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>365</v>
       </c>
@@ -9444,7 +9462,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>366</v>
       </c>
@@ -9558,7 +9576,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>367</v>
       </c>
@@ -9670,7 +9688,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>368</v>
       </c>
@@ -9784,7 +9802,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>369</v>
       </c>
@@ -9898,7 +9916,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>370</v>
       </c>
@@ -10012,7 +10030,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>371</v>
       </c>
@@ -10126,7 +10144,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>372</v>
       </c>
@@ -10240,7 +10258,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>373</v>
       </c>
@@ -10261,7 +10279,7 @@
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
@@ -10356,7 +10374,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>376</v>
       </c>
@@ -10468,7 +10486,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>378</v>
       </c>
@@ -10580,7 +10598,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>381</v>
       </c>
@@ -10696,7 +10714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>384</v>
       </c>
@@ -10810,7 +10828,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>388</v>
       </c>
@@ -10922,7 +10940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>390</v>
       </c>
@@ -11034,7 +11052,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>393</v>
       </c>
@@ -11150,7 +11168,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>396</v>
       </c>
@@ -11262,7 +11280,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>398</v>
       </c>
@@ -11374,7 +11392,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>401</v>
       </c>
@@ -11490,7 +11508,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>404</v>
       </c>
@@ -11604,7 +11622,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>406</v>
       </c>
@@ -11718,7 +11736,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>410</v>
       </c>
@@ -11832,7 +11850,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>413</v>
       </c>
@@ -11948,7 +11966,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>416</v>
       </c>
@@ -12064,7 +12082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>419</v>
       </c>
@@ -12180,7 +12198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>423</v>
       </c>
@@ -12294,7 +12312,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>425</v>
       </c>
@@ -12406,7 +12424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>428</v>
       </c>
@@ -12520,7 +12538,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>430</v>
       </c>
@@ -12632,7 +12650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>431</v>
       </c>
@@ -12746,7 +12764,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>432</v>
       </c>
@@ -12860,7 +12878,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>433</v>
       </c>
@@ -12974,7 +12992,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>434</v>
       </c>
@@ -13088,7 +13106,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>435</v>
       </c>
@@ -13202,7 +13220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>437</v>
       </c>
@@ -13223,7 +13241,7 @@
         <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>77</v>
@@ -13318,7 +13336,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>440</v>
       </c>
@@ -13430,7 +13448,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>442</v>
       </c>
@@ -13542,7 +13560,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>445</v>
       </c>
@@ -13658,7 +13676,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>448</v>
       </c>
@@ -13772,7 +13790,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>452</v>
       </c>
@@ -13884,7 +13902,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
         <v>454</v>
       </c>
@@ -13996,7 +14014,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
         <v>457</v>
       </c>
@@ -14112,7 +14130,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
         <v>460</v>
       </c>
@@ -14224,7 +14242,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
         <v>462</v>
       </c>
@@ -14336,7 +14354,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
         <v>465</v>
       </c>
@@ -14452,7 +14470,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
         <v>468</v>
       </c>
@@ -14566,7 +14584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
         <v>470</v>
       </c>
@@ -14680,7 +14698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
         <v>474</v>
       </c>
@@ -14794,7 +14812,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>477</v>
       </c>
@@ -14910,7 +14928,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
         <v>480</v>
       </c>
@@ -15026,7 +15044,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>483</v>
       </c>
@@ -15142,7 +15160,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>487</v>
       </c>
@@ -15256,7 +15274,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
         <v>489</v>
       </c>
@@ -15368,7 +15386,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
         <v>492</v>
       </c>
@@ -15482,7 +15500,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
         <v>494</v>
       </c>
@@ -15594,7 +15612,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
         <v>495</v>
       </c>
@@ -15708,7 +15726,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
         <v>496</v>
       </c>
@@ -15822,7 +15840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
         <v>497</v>
       </c>
@@ -15936,7 +15954,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
         <v>498</v>
       </c>
@@ -16050,7 +16068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
         <v>499</v>
       </c>
@@ -16164,7 +16182,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
         <v>501</v>
       </c>
@@ -16185,7 +16203,7 @@
         <v>88</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>77</v>
@@ -16280,7 +16298,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
         <v>504</v>
       </c>
@@ -16392,7 +16410,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
         <v>506</v>
       </c>
@@ -16504,7 +16522,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
         <v>509</v>
       </c>
@@ -16620,7 +16638,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
         <v>512</v>
       </c>
@@ -16734,7 +16752,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
         <v>516</v>
       </c>
@@ -16846,7 +16864,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
         <v>518</v>
       </c>
@@ -16958,7 +16976,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
         <v>521</v>
       </c>
@@ -17074,7 +17092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
         <v>524</v>
       </c>
@@ -17186,7 +17204,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
         <v>526</v>
       </c>
@@ -17298,7 +17316,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
         <v>529</v>
       </c>
@@ -17414,7 +17432,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
         <v>532</v>
       </c>
@@ -17528,7 +17546,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
         <v>534</v>
       </c>
@@ -17642,7 +17660,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
         <v>538</v>
       </c>
@@ -17756,7 +17774,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
         <v>541</v>
       </c>
@@ -17872,7 +17890,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
         <v>544</v>
       </c>
@@ -17988,7 +18006,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
         <v>547</v>
       </c>
@@ -18104,7 +18122,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
         <v>551</v>
       </c>
@@ -18218,7 +18236,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
         <v>553</v>
       </c>
@@ -18330,7 +18348,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
         <v>556</v>
       </c>
@@ -18444,7 +18462,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
         <v>558</v>
       </c>
@@ -18556,7 +18574,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
         <v>559</v>
       </c>
@@ -18670,7 +18688,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
         <v>560</v>
       </c>
@@ -18784,7 +18802,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
         <v>561</v>
       </c>
@@ -18898,7 +18916,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
         <v>562</v>
       </c>
@@ -19012,7 +19030,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
         <v>563</v>
       </c>
@@ -19126,7 +19144,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
         <v>565</v>
       </c>
@@ -19147,7 +19165,7 @@
         <v>88</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>77</v>
@@ -19242,7 +19260,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
         <v>568</v>
       </c>
@@ -19354,7 +19372,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
         <v>570</v>
       </c>
@@ -19466,7 +19484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
         <v>573</v>
       </c>
@@ -19582,7 +19600,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
         <v>576</v>
       </c>
@@ -19696,7 +19714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
         <v>580</v>
       </c>
@@ -19808,7 +19826,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
         <v>582</v>
       </c>
@@ -19920,7 +19938,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
         <v>585</v>
       </c>
@@ -20036,7 +20054,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
         <v>588</v>
       </c>
@@ -20148,7 +20166,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
         <v>590</v>
       </c>
@@ -20260,7 +20278,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
         <v>593</v>
       </c>
@@ -20376,7 +20394,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
         <v>596</v>
       </c>
@@ -20490,7 +20508,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
         <v>598</v>
       </c>
@@ -20604,7 +20622,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
         <v>602</v>
       </c>
@@ -20718,7 +20736,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
         <v>605</v>
       </c>
@@ -20834,7 +20852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
         <v>608</v>
       </c>
@@ -20950,7 +20968,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
         <v>611</v>
       </c>
@@ -21066,7 +21084,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
         <v>615</v>
       </c>
@@ -21180,7 +21198,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
         <v>617</v>
       </c>
@@ -21292,7 +21310,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
         <v>620</v>
       </c>
@@ -21406,7 +21424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
         <v>622</v>
       </c>
@@ -21518,7 +21536,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
         <v>623</v>
       </c>
@@ -21632,7 +21650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
         <v>624</v>
       </c>
@@ -21746,7 +21764,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
         <v>625</v>
       </c>
@@ -21860,7 +21878,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
         <v>626</v>
       </c>
@@ -21974,7 +21992,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
         <v>627</v>
       </c>
@@ -22088,7 +22106,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
         <v>629</v>
       </c>
@@ -22109,7 +22127,7 @@
         <v>88</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>77</v>
@@ -22204,7 +22222,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
         <v>632</v>
       </c>
@@ -22316,7 +22334,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
         <v>634</v>
       </c>
@@ -22428,7 +22446,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
         <v>637</v>
       </c>
@@ -22544,7 +22562,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
         <v>640</v>
       </c>
@@ -22658,7 +22676,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
         <v>644</v>
       </c>
@@ -22770,7 +22788,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
         <v>646</v>
       </c>
@@ -22882,7 +22900,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
         <v>649</v>
       </c>
@@ -22998,7 +23016,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
         <v>652</v>
       </c>
@@ -23110,7 +23128,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
         <v>654</v>
       </c>
@@ -23222,7 +23240,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
         <v>657</v>
       </c>
@@ -23338,7 +23356,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
         <v>660</v>
       </c>
@@ -23452,7 +23470,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
         <v>662</v>
       </c>
@@ -23566,7 +23584,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
         <v>665</v>
       </c>
@@ -23680,7 +23698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
         <v>668</v>
       </c>
@@ -23796,7 +23814,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
         <v>671</v>
       </c>
@@ -23912,7 +23930,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
         <v>674</v>
       </c>
@@ -24028,7 +24046,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
         <v>678</v>
       </c>
@@ -24142,7 +24160,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
         <v>680</v>
       </c>
@@ -24254,7 +24272,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
         <v>683</v>
       </c>
@@ -24368,7 +24386,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
         <v>685</v>
       </c>
@@ -24480,7 +24498,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
         <v>686</v>
       </c>
@@ -24594,7 +24612,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
         <v>687</v>
       </c>
@@ -24708,7 +24726,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
         <v>688</v>
       </c>
@@ -24822,7 +24840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
         <v>689</v>
       </c>
@@ -24936,7 +24954,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
         <v>690</v>
       </c>
@@ -25050,7 +25068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
         <v>692</v>
       </c>
@@ -25168,7 +25186,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
         <v>699</v>
       </c>
@@ -25284,7 +25302,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
         <v>708</v>
       </c>
@@ -25396,7 +25414,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
         <v>711</v>
       </c>
@@ -25508,7 +25526,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
         <v>714</v>
       </c>
@@ -25624,7 +25642,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
         <v>725</v>
       </c>
@@ -25740,7 +25758,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
         <v>733</v>
       </c>
@@ -25854,7 +25872,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
         <v>742</v>
       </c>
@@ -25968,7 +25986,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
         <v>751</v>
       </c>
@@ -26080,7 +26098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
         <v>758</v>
       </c>
@@ -26192,7 +26210,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
         <v>764</v>
       </c>
@@ -26306,7 +26324,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
         <v>771</v>
       </c>
@@ -26422,7 +26440,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
         <v>780</v>
       </c>
@@ -26538,7 +26556,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
         <v>789</v>
       </c>
@@ -26652,7 +26670,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
         <v>798</v>
       </c>
@@ -26766,7 +26784,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
         <v>806</v>
       </c>
@@ -26880,7 +26898,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
         <v>813</v>
       </c>
@@ -26992,7 +27010,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
         <v>820</v>
       </c>
@@ -27104,7 +27122,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
         <v>823</v>
       </c>
@@ -27216,7 +27234,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
         <v>826</v>
       </c>
@@ -27332,7 +27350,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
         <v>832</v>
       </c>
@@ -27446,7 +27464,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
         <v>836</v>
       </c>
@@ -27556,7 +27574,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
         <v>840</v>
       </c>
@@ -27668,7 +27686,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
         <v>841</v>
       </c>
@@ -27782,7 +27800,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
         <v>842</v>
       </c>
@@ -27898,7 +27916,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
         <v>844</v>
       </c>
@@ -28010,7 +28028,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
         <v>845</v>
       </c>
@@ -28124,7 +28142,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
         <v>846</v>
       </c>
@@ -28240,7 +28258,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
         <v>848</v>
       </c>
@@ -28354,7 +28372,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
         <v>850</v>
       </c>
@@ -28468,7 +28486,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
         <v>851</v>
       </c>
@@ -28582,7 +28600,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
         <v>854</v>
       </c>
@@ -28698,7 +28716,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
         <v>857</v>
       </c>
@@ -28814,7 +28832,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
         <v>860</v>
       </c>
@@ -28928,7 +28946,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
         <v>865</v>
       </c>
@@ -29040,7 +29058,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
         <v>868</v>
       </c>
@@ -29157,6 +29175,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN229">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI228">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/StructureDefinition-br-core-practitioner.xlsx
+++ b/docs/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T10:02:10-03:00</t>
+    <t>2026-09-25T17:16:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-br-core-practitioner.xlsx
+++ b/docs/StructureDefinition-br-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T17:16:20-03:00</t>
+    <t>2026-09-28T11:57:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
